--- a/research/traditional_assets/database/data/bermuda/bermuda_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.252</v>
+        <v>0.19695</v>
       </c>
       <c r="E2">
-        <v>0.213</v>
+        <v>0.21595</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.07049067035245335</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.07049067035245335</v>
       </c>
       <c r="I2">
-        <v>0.9750000000000001</v>
+        <v>0.9708592490209629</v>
       </c>
       <c r="J2">
-        <v>0.9750000000000001</v>
+        <v>0.8956126937287452</v>
       </c>
       <c r="K2">
-        <v>214.2</v>
+        <v>433.6</v>
       </c>
       <c r="L2">
-        <v>0.9394736842105262</v>
+        <v>0.9988481916609075</v>
       </c>
       <c r="M2">
-        <v>58.7</v>
+        <v>40.69</v>
       </c>
       <c r="N2">
-        <v>0.05799822151961269</v>
+        <v>0.03083042885285649</v>
       </c>
       <c r="O2">
-        <v>0.2740429505135388</v>
+        <v>0.09384225092250922</v>
       </c>
       <c r="P2">
-        <v>11.5</v>
+        <v>25.67</v>
       </c>
       <c r="Q2">
-        <v>0.01136251358561407</v>
+        <v>0.01944991665403849</v>
       </c>
       <c r="R2">
-        <v>0.05368814192343604</v>
+        <v>0.05920202952029521</v>
       </c>
       <c r="S2">
-        <v>47.2</v>
+        <v>15.02</v>
       </c>
       <c r="T2">
-        <v>0.8040885860306644</v>
+        <v>0.3691324649791104</v>
       </c>
       <c r="U2">
-        <v>236.9</v>
+        <v>165.69</v>
       </c>
       <c r="V2">
-        <v>0.2340677798636498</v>
+        <v>0.1255417487498106</v>
       </c>
       <c r="W2">
-        <v>0.250029181743901</v>
+        <v>0.3648964896489649</v>
       </c>
       <c r="X2">
-        <v>0.04990546078544718</v>
+        <v>0.08080896316055915</v>
       </c>
       <c r="Y2">
-        <v>0.2001237209584538</v>
+        <v>0.2840875264884057</v>
       </c>
       <c r="Z2">
-        <v>0.4278476261962844</v>
+        <v>0.4240715558473225</v>
       </c>
       <c r="AA2">
-        <v>0.4171514355413773</v>
+        <v>0.08366270088076562</v>
       </c>
       <c r="AB2">
-        <v>0.04990546078544718</v>
+        <v>0.08078498133982727</v>
       </c>
       <c r="AC2">
-        <v>0.3672459747559302</v>
+        <v>0.00287771954093835</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="AG2">
-        <v>-236.9</v>
+        <v>-164.266</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.001077788474929308</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.000915977110864106</v>
       </c>
       <c r="AJ2">
-        <v>-0.3055985552115583</v>
+        <v>-0.1421559209854492</v>
       </c>
       <c r="AK2">
-        <v>-0.2710216222400183</v>
+        <v>-0.1182676786657969</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-1.746</v>
+      </c>
+      <c r="AN2">
+        <v>0.08736196319018404</v>
+      </c>
+      <c r="AO2">
+        <v>105362.5</v>
+      </c>
+      <c r="AP2">
+        <v>-10.07766871165644</v>
+      </c>
+      <c r="AQ2">
+        <v>-241.3802978235968</v>
       </c>
     </row>
     <row r="3">
@@ -710,10 +722,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.252</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="E3">
-        <v>0.213</v>
+        <v>0.459</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,67 +734,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9750000000000001</v>
+        <v>0.9871390439213783</v>
       </c>
       <c r="J3">
-        <v>0.9750000000000001</v>
+        <v>0.9871390439213783</v>
       </c>
       <c r="K3">
-        <v>214.2</v>
+        <v>405.4</v>
       </c>
       <c r="L3">
-        <v>0.9394736842105262</v>
+        <v>0.9837418102402329</v>
       </c>
       <c r="M3">
-        <v>58.7</v>
+        <v>23.27</v>
       </c>
       <c r="N3">
-        <v>0.05799822151961269</v>
+        <v>0.02609622070202983</v>
       </c>
       <c r="O3">
-        <v>0.2740429505135388</v>
+        <v>0.05740009866798224</v>
       </c>
       <c r="P3">
-        <v>11.5</v>
+        <v>9.77</v>
       </c>
       <c r="Q3">
-        <v>0.01136251358561407</v>
+        <v>0.01095659975328025</v>
       </c>
       <c r="R3">
-        <v>0.05368814192343604</v>
+        <v>0.02409965466206216</v>
       </c>
       <c r="S3">
-        <v>47.2</v>
+        <v>13.5</v>
       </c>
       <c r="T3">
-        <v>0.8040885860306644</v>
+        <v>0.5801461108723679</v>
       </c>
       <c r="U3">
-        <v>236.9</v>
+        <v>118.1</v>
       </c>
       <c r="V3">
-        <v>0.2340677798636498</v>
+        <v>0.1324436469664685</v>
       </c>
       <c r="W3">
-        <v>0.250029181743901</v>
+        <v>0.3648964896489649</v>
       </c>
       <c r="X3">
-        <v>0.04990546078544718</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y3">
-        <v>0.2001237209584538</v>
+        <v>0.2841310358218051</v>
       </c>
       <c r="Z3">
-        <v>0.4278476261962844</v>
+        <v>0.4714563551081112</v>
       </c>
       <c r="AA3">
-        <v>0.4171514355413773</v>
+        <v>0.4653929756320787</v>
       </c>
       <c r="AB3">
-        <v>0.04990546078544718</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AC3">
-        <v>0.3672459747559302</v>
+        <v>0.384627521804919</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-236.9</v>
+        <v>-118.1</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,16 +815,251 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3055985552115583</v>
+        <v>-0.1526628748707342</v>
       </c>
       <c r="AK3">
-        <v>-0.2710216222400183</v>
+        <v>-0.09511920103092782</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hotung Investment Holdings Limited (SGX:BLS)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0441</v>
+      </c>
+      <c r="E4">
+        <v>-0.0271</v>
+      </c>
+      <c r="G4">
+        <v>1.390909090909091</v>
+      </c>
+      <c r="H4">
+        <v>1.390909090909091</v>
+      </c>
+      <c r="I4">
+        <v>0.740909090909091</v>
+      </c>
+      <c r="J4">
+        <v>0.5686363636363637</v>
+      </c>
+      <c r="K4">
+        <v>10.8</v>
+      </c>
+      <c r="L4">
+        <v>0.490909090909091</v>
+      </c>
+      <c r="M4">
+        <v>17.42</v>
+      </c>
+      <c r="N4">
+        <v>0.1456521739130435</v>
+      </c>
+      <c r="O4">
+        <v>1.612962962962963</v>
+      </c>
+      <c r="P4">
+        <v>15.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.1329431438127091</v>
+      </c>
+      <c r="R4">
+        <v>1.472222222222222</v>
+      </c>
+      <c r="S4">
+        <v>1.520000000000001</v>
+      </c>
+      <c r="T4">
+        <v>0.08725602755453508</v>
+      </c>
+      <c r="U4">
+        <v>47</v>
+      </c>
+      <c r="V4">
+        <v>0.3929765886287626</v>
+      </c>
+      <c r="W4">
+        <v>0.04972375690607735</v>
+      </c>
+      <c r="X4">
+        <v>0.08080896316055915</v>
+      </c>
+      <c r="Y4">
+        <v>-0.03108520625448179</v>
+      </c>
+      <c r="Z4">
+        <v>0.1471286506296438</v>
+      </c>
+      <c r="AA4">
+        <v>0.08366270088076562</v>
+      </c>
+      <c r="AB4">
+        <v>0.08078498133982727</v>
+      </c>
+      <c r="AC4">
+        <v>0.00287771954093835</v>
+      </c>
+      <c r="AD4">
+        <v>0.124</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.124</v>
+      </c>
+      <c r="AG4">
+        <v>-46.876</v>
+      </c>
+      <c r="AH4">
+        <v>0.001035715478934884</v>
+      </c>
+      <c r="AI4">
+        <v>0.0005989643712806244</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.6445740058302625</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2929310603409488</v>
+      </c>
+      <c r="AL4">
+        <v>0.004</v>
+      </c>
+      <c r="AM4">
+        <v>0.004</v>
+      </c>
+      <c r="AN4">
+        <v>0.007607361963190184</v>
+      </c>
+      <c r="AO4">
+        <v>4075</v>
+      </c>
+      <c r="AP4">
+        <v>-2.875828220858895</v>
+      </c>
+      <c r="AQ4">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ST Energy Transition I Ltd. (NYSE:STET)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>17.4</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.59</v>
+      </c>
+      <c r="V5">
+        <v>0.001912479740680713</v>
+      </c>
+      <c r="W5">
+        <v>915.7894736842105</v>
+      </c>
+      <c r="X5">
+        <v>0.08094229366500515</v>
+      </c>
+      <c r="Y5">
+        <v>915.7085313905455</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-86.84210526315789</v>
+      </c>
+      <c r="AB5">
+        <v>0.08089282751009221</v>
+      </c>
+      <c r="AC5">
+        <v>-86.92299809066799</v>
+      </c>
+      <c r="AD5">
+        <v>1.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.3</v>
+      </c>
+      <c r="AG5">
+        <v>0.7100000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.004196255648805681</v>
+      </c>
+      <c r="AI5">
+        <v>-0.1074380165289256</v>
+      </c>
+      <c r="AJ5">
+        <v>0.002296174121147441</v>
+      </c>
+      <c r="AK5">
+        <v>-0.05594956658786447</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-1.75</v>
+      </c>
+      <c r="AQ5">
+        <v>0.9428571428571428</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.19695</v>
+        <v>-0.027915</v>
       </c>
       <c r="E2">
-        <v>0.21595</v>
+        <v>-0.05574999999999999</v>
       </c>
       <c r="G2">
-        <v>0.07049067035245335</v>
+        <v>0.03256704980842912</v>
       </c>
       <c r="H2">
-        <v>0.07049067035245335</v>
+        <v>0.03256704980842912</v>
       </c>
       <c r="I2">
-        <v>0.9708592490209629</v>
+        <v>0.8627394636015326</v>
       </c>
       <c r="J2">
-        <v>0.8956126937287452</v>
+        <v>0.7681862290410593</v>
       </c>
       <c r="K2">
-        <v>433.6</v>
+        <v>86.77</v>
       </c>
       <c r="L2">
-        <v>0.9988481916609075</v>
+        <v>0.8311302681992336</v>
       </c>
       <c r="M2">
-        <v>40.69</v>
+        <v>24.22</v>
       </c>
       <c r="N2">
-        <v>0.03083042885285649</v>
+        <v>0.0198394495412844</v>
       </c>
       <c r="O2">
-        <v>0.09384225092250922</v>
+        <v>0.2791287311282701</v>
       </c>
       <c r="P2">
-        <v>25.67</v>
+        <v>17.86</v>
       </c>
       <c r="Q2">
-        <v>0.01944991665403849</v>
+        <v>0.01462975098296199</v>
       </c>
       <c r="R2">
-        <v>0.05920202952029521</v>
+        <v>0.2058315085859168</v>
       </c>
       <c r="S2">
-        <v>15.02</v>
+        <v>6.360000000000001</v>
       </c>
       <c r="T2">
-        <v>0.3691324649791104</v>
+        <v>0.2625928984310488</v>
       </c>
       <c r="U2">
-        <v>165.69</v>
+        <v>429.7</v>
       </c>
       <c r="V2">
-        <v>0.1255417487498106</v>
+        <v>0.3519823066841415</v>
       </c>
       <c r="W2">
-        <v>0.3648964896489649</v>
+        <v>0.04603582889162106</v>
       </c>
       <c r="X2">
-        <v>0.08080896316055915</v>
+        <v>0.06944773502899754</v>
       </c>
       <c r="Y2">
-        <v>0.2840875264884057</v>
+        <v>-0.02341190613737647</v>
       </c>
       <c r="Z2">
-        <v>0.4240715558473225</v>
+        <v>0.07465546929972597</v>
       </c>
       <c r="AA2">
-        <v>0.08366270088076562</v>
+        <v>0.05540706896259304</v>
       </c>
       <c r="AB2">
-        <v>0.08078498133982727</v>
+        <v>0.06903383937987051</v>
       </c>
       <c r="AC2">
-        <v>0.00287771954093835</v>
+        <v>-0.01362677041727747</v>
       </c>
       <c r="AD2">
-        <v>1.424</v>
+        <v>60.241</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.424</v>
+        <v>60.241</v>
       </c>
       <c r="AG2">
-        <v>-164.266</v>
+        <v>-369.459</v>
       </c>
       <c r="AH2">
-        <v>0.001077788474929308</v>
+        <v>0.04702503666939622</v>
       </c>
       <c r="AI2">
-        <v>0.000915977110864106</v>
+        <v>0.03450740974749404</v>
       </c>
       <c r="AJ2">
-        <v>-0.1421559209854492</v>
+        <v>-0.4339729908462062</v>
       </c>
       <c r="AK2">
-        <v>-0.1182676786657969</v>
+        <v>-0.2807351746640113</v>
       </c>
       <c r="AL2">
-        <v>0.004</v>
+        <v>1.952</v>
       </c>
       <c r="AM2">
-        <v>-1.746</v>
+        <v>1.952</v>
       </c>
       <c r="AN2">
-        <v>0.08736196319018404</v>
+        <v>6.569356597600873</v>
       </c>
       <c r="AO2">
-        <v>105362.5</v>
+        <v>46.14241803278689</v>
       </c>
       <c r="AP2">
-        <v>-10.07766871165644</v>
+        <v>-40.28996728462377</v>
       </c>
       <c r="AQ2">
-        <v>-241.3802978235968</v>
+        <v>46.14241803278689</v>
       </c>
     </row>
     <row r="3">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.4379999999999999</v>
+        <v>-0.00233</v>
       </c>
       <c r="E3">
-        <v>0.459</v>
+        <v>-0.0105</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,97 +734,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9871390439213783</v>
+        <v>0.88998899889989</v>
       </c>
       <c r="J3">
-        <v>0.9871390439213783</v>
+        <v>0.88998899889989</v>
       </c>
       <c r="K3">
-        <v>405.4</v>
+        <v>80</v>
       </c>
       <c r="L3">
-        <v>0.9837418102402329</v>
+        <v>0.88008800880088</v>
       </c>
       <c r="M3">
-        <v>23.27</v>
+        <v>16.46</v>
       </c>
       <c r="N3">
-        <v>0.02609622070202983</v>
+        <v>0.01482749301864697</v>
       </c>
       <c r="O3">
-        <v>0.05740009866798224</v>
+        <v>0.20575</v>
       </c>
       <c r="P3">
-        <v>9.77</v>
+        <v>10.1</v>
       </c>
       <c r="Q3">
-        <v>0.01095659975328025</v>
+        <v>0.009098279434285201</v>
       </c>
       <c r="R3">
-        <v>0.02409965466206216</v>
+        <v>0.12625</v>
       </c>
       <c r="S3">
-        <v>13.5</v>
+        <v>6.360000000000001</v>
       </c>
       <c r="T3">
-        <v>0.5801461108723679</v>
+        <v>0.3863912515188336</v>
       </c>
       <c r="U3">
-        <v>118.1</v>
+        <v>375.9</v>
       </c>
       <c r="V3">
-        <v>0.1324436469664685</v>
+        <v>0.3386181425096838</v>
       </c>
       <c r="W3">
-        <v>0.3648964896489649</v>
+        <v>0.05883650805324703</v>
       </c>
       <c r="X3">
-        <v>0.08076545382715974</v>
+        <v>0.07025113029946142</v>
       </c>
       <c r="Y3">
-        <v>0.2841310358218051</v>
+        <v>-0.01141462224621439</v>
       </c>
       <c r="Z3">
-        <v>0.4714563551081112</v>
+        <v>0.07321198453608246</v>
       </c>
       <c r="AA3">
-        <v>0.4653929756320787</v>
+        <v>0.06515786082474226</v>
       </c>
       <c r="AB3">
-        <v>0.08076545382715974</v>
+        <v>0.06942866374141261</v>
       </c>
       <c r="AC3">
-        <v>0.384627521804919</v>
+        <v>-0.004270802916670355</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="AG3">
-        <v>-118.1</v>
+        <v>-315.7</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.05143980176023243</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.03894675551530051</v>
       </c>
       <c r="AJ3">
-        <v>-0.1526628748707342</v>
+        <v>-0.3974068479355489</v>
       </c>
       <c r="AK3">
-        <v>-0.09511920103092782</v>
+        <v>-0.2698751923405711</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.95</v>
+      </c>
+      <c r="AO3">
+        <v>41.48717948717949</v>
+      </c>
+      <c r="AQ3">
+        <v>41.48717948717949</v>
       </c>
     </row>
     <row r="4">
@@ -844,222 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0441</v>
+        <v>-0.0535</v>
       </c>
       <c r="E4">
-        <v>-0.0271</v>
+        <v>-0.101</v>
       </c>
       <c r="G4">
-        <v>1.390909090909091</v>
+        <v>0.2518518518518518</v>
       </c>
       <c r="H4">
-        <v>1.390909090909091</v>
+        <v>0.2518518518518518</v>
       </c>
       <c r="I4">
-        <v>0.740909090909091</v>
+        <v>0.6792592592592592</v>
       </c>
       <c r="J4">
-        <v>0.5686363636363637</v>
+        <v>0.5303703703703704</v>
       </c>
       <c r="K4">
-        <v>10.8</v>
+        <v>6.77</v>
       </c>
       <c r="L4">
-        <v>0.490909090909091</v>
+        <v>0.5014814814814814</v>
       </c>
       <c r="M4">
-        <v>17.42</v>
+        <v>7.76</v>
       </c>
       <c r="N4">
-        <v>0.1456521739130435</v>
+        <v>0.07009936766034326</v>
       </c>
       <c r="O4">
-        <v>1.612962962962963</v>
+        <v>1.146233382570162</v>
       </c>
       <c r="P4">
-        <v>15.9</v>
+        <v>7.76</v>
       </c>
       <c r="Q4">
-        <v>0.1329431438127091</v>
+        <v>0.07009936766034326</v>
       </c>
       <c r="R4">
-        <v>1.472222222222222</v>
+        <v>1.146233382570162</v>
       </c>
       <c r="S4">
-        <v>1.520000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.08725602755453508</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>47</v>
+        <v>53.8</v>
       </c>
       <c r="V4">
-        <v>0.3929765886287626</v>
+        <v>0.4859981933152664</v>
       </c>
       <c r="W4">
-        <v>0.04972375690607735</v>
+        <v>0.03323514972999509</v>
       </c>
       <c r="X4">
-        <v>0.08080896316055915</v>
+        <v>0.06864433975853364</v>
       </c>
       <c r="Y4">
-        <v>-0.03108520625448179</v>
+        <v>-0.03540919002853855</v>
       </c>
       <c r="Z4">
-        <v>0.1471286506296438</v>
+        <v>0.08608376268938428</v>
       </c>
       <c r="AA4">
-        <v>0.08366270088076562</v>
+        <v>0.04565627710044382</v>
       </c>
       <c r="AB4">
-        <v>0.08078498133982727</v>
+        <v>0.06863901501832839</v>
       </c>
       <c r="AC4">
-        <v>0.00287771954093835</v>
+        <v>-0.02298273791788458</v>
       </c>
       <c r="AD4">
-        <v>0.124</v>
+        <v>0.041</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.124</v>
+        <v>0.041</v>
       </c>
       <c r="AG4">
-        <v>-46.876</v>
+        <v>-53.759</v>
       </c>
       <c r="AH4">
-        <v>0.001035715478934884</v>
+        <v>0.0003702332469455757</v>
       </c>
       <c r="AI4">
-        <v>0.0005989643712806244</v>
+        <v>0.0002049579836133593</v>
       </c>
       <c r="AJ4">
-        <v>-0.6445740058302625</v>
+        <v>-0.9441175954057709</v>
       </c>
       <c r="AK4">
-        <v>-0.2929310603409488</v>
+        <v>-0.3676055278615437</v>
       </c>
       <c r="AL4">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM4">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AN4">
-        <v>0.007607361963190184</v>
+        <v>0.004471101417666303</v>
       </c>
       <c r="AO4">
-        <v>4075</v>
+        <v>4585</v>
       </c>
       <c r="AP4">
-        <v>-2.875828220858895</v>
+        <v>-5.862486368593239</v>
       </c>
       <c r="AQ4">
-        <v>4075</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ST Energy Transition I Ltd. (NYSE:STET)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>17.4</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.59</v>
-      </c>
-      <c r="V5">
-        <v>0.001912479740680713</v>
-      </c>
-      <c r="W5">
-        <v>915.7894736842105</v>
-      </c>
-      <c r="X5">
-        <v>0.08094229366500515</v>
-      </c>
-      <c r="Y5">
-        <v>915.7085313905455</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>-86.84210526315789</v>
-      </c>
-      <c r="AB5">
-        <v>0.08089282751009221</v>
-      </c>
-      <c r="AC5">
-        <v>-86.92299809066799</v>
-      </c>
-      <c r="AD5">
-        <v>1.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1.3</v>
-      </c>
-      <c r="AG5">
-        <v>0.7100000000000001</v>
-      </c>
-      <c r="AH5">
-        <v>0.004196255648805681</v>
-      </c>
-      <c r="AI5">
-        <v>-0.1074380165289256</v>
-      </c>
-      <c r="AJ5">
-        <v>0.002296174121147441</v>
-      </c>
-      <c r="AK5">
-        <v>-0.05594956658786447</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-1.75</v>
-      </c>
-      <c r="AQ5">
-        <v>0.9428571428571428</v>
+        <v>4585</v>
       </c>
     </row>
   </sheetData>
